--- a/vyntic-30-day-calendar.xlsx
+++ b/vyntic-30-day-calendar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Calendar'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Calendar'!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,7 +86,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +111,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F5EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -196,15 +201,18 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -711,45 +719,45 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Sat and Sun: no new posts, engagement only (15 minutes)</t>
+          <t>Sat: service spotlight image (LinkedIn, Instagram, Facebook), plus 15 minutes of engagement</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sun: no new post, engagement only (15 minutes)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>WHY THESE TOPICS (trending this month)</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Week 1: WordPress 7.1.3 security release (6 Oct) and website speed / Core Web Vitals, with the launch of the free Speed Optimizer plugin.</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>OUR SERVICES IN THIS PLAN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Week 2: AI search. Google AI Overviews and AI Mode, Search Console's new AI performance reports, GEO, getting recommended by ChatGPT.</t>
+          <t>Service spotlights (Saturdays): Website design and development (17 Oct), Local SEO + Google Business Profile + GoHighLevel (24 Oct), Website redesign and migration (31 Oct), WordPress, WooCommerce and Shopify development (7 Nov).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Week 3: Google's September 2026 spam update (finished 8 Oct), Google Business Profile before the holidays, Halloween 'website horror story'.</t>
+          <t>Promoted at the end of posts: care plans (Day 5), AI search visibility (Days 8 and 26), SEO services (Day 12), free audit (Day 15), Google Business Profile optimization (Day 19), speed optimization (Day 17), landing pages (Day 22), online stores (Day 24), website cost calculator (Day 29), free plugins (Days 1, 3, 4).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Week 4 and 5: Black Friday (27 Nov) and Small Business Saturday (28 Nov): checkout, AI shopping, website costs.</t>
+          <t>Every Pinterest pin description also names the matching service.</t>
         </is>
       </c>
     </row>
@@ -759,52 +767,52 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>TIMES</t>
+          <t>WHY THESE TOPICS (trending this month)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Times are set for a US audience (US Eastern). The Pakistan time is shown next to it. US clocks change on 1 November, so the Pakistan time moves one hour later from then on; the sheet already accounts for it.</t>
+          <t>Week 1: WordPress 7.1.3 security release (6 Oct) and website speed / Core Web Vitals, with the launch of the free Speed Optimizer plugin.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Week 2: AI search. Google AI Overviews and AI Mode, Search Console's new AI performance reports, GEO, getting recommended by ChatGPT.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>DAILY 15-MINUTE ENGAGEMENT (every day, including weekends)</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Week 3: Google's September 2026 spam update (finished 8 Oct), Google Business Profile before the holidays, Halloween 'website horror story'.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Reply to every comment and DM, especially in the first hour after a post.</t>
+          <t>Week 4 and 5: Black Friday (27 Nov) and Small Business Saturday (28 Nov): checkout, AI shopping, website costs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Comment helpfully on 5 posts from small business owners, marketers and WordPress users.</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Answer 1 question in a Facebook group, Quora or Reddit, and link to a vyntic.studio article only when it truly helps.</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TIMES</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>When someone comments a keyword (SPEED, AI, CHECKOUT), reply and send the link by DM the same day.</t>
+          <t>Times are set for a US audience (US Eastern). The Pakistan time is shown next to it. US clocks change on 1 November, so the Pakistan time moves one hour later from then on; the sheet already accounts for it.</t>
         </is>
       </c>
     </row>
@@ -814,33 +822,71 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>BEFORE YOU POST</t>
+          <t>DAILY 15-MINUTE ENGAGEMENT (every day, including weekends)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Every link points to a live vyntic.studio page. Open it once before posting.</t>
+          <t>Reply to every comment and DM, especially in the first hour after a post.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Reels: two versions in each reel folder. reel-voiceover.mp4 (recommended) and reel-silent.mp4 (music only). Watch the voice version once with sound before posting.</t>
+          <t>Comment helpfully on 5 posts from small business owners, marketers and WordPress users.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Instagram captions say "Link in bio": keep the bio link pointing to vyntic.studio/free-audit/ and the latest article.</t>
+          <t>Answer 1 question in a Facebook group, Quora or Reddit, and link to a vyntic.studio article only when it truly helps.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>When someone comments a keyword (SPEED, AI, CHECKOUT), reply and send the link by DM the same day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>BEFORE YOU POST</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Every link points to a live vyntic.studio page. Open it once before posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Reels: two versions in each reel folder. reel-voiceover.mp4 (recommended) and reel-silent.mp4 (music only). Watch the voice version once with sound before posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Instagram captions say "Link in bio": keep the bio link pointing to vyntic.studio/free-audit/ and the latest article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Numbers used in posts come from public sources (Ahrefs, Google, WordPress.org) or vyntic.studio's own price guide. Do not change them to client results unless they are real.</t>
         </is>
@@ -1164,21 +1210,41 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Engage only</t>
+          <t>Spotlight</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>No new post. 15 minutes: reply to comments and DMs, comment on 5 posts from small business owners, answer 1 question in a Facebook group, Quora or Reddit.</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
+          <t>Service spotlight: website design and development</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Week 1 (Oct 12 to Oct 18)/Day 06 Sat Oct 17 Spotlight Service spotlight website design and</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/web-design/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1189,7 +1255,7 @@
           <t>Sun 18 Oct</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Engage only</t>
         </is>
@@ -1441,21 +1507,41 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Engage only</t>
+          <t>Spotlight</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>No new post. 15 minutes: reply to comments and DMs, comment on 5 posts from small business owners, answer 1 question in a Facebook group, Quora or Reddit.</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
+          <t>Service spotlight: local SEO and lead follow-up</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Week 2 (Oct 19 to Oct 25)/Day 13 Sat Oct 24 Spotlight Service spotlight local SEO and lead</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/local-seo/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1466,7 +1552,7 @@
           <t>Sun 25 Oct</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Engage only</t>
         </is>
@@ -1703,7 +1789,7 @@
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>https://vyntic.studio/google-business-profile-guide/</t>
+          <t>https://vyntic.studio/services/google-business-profile-optimization/</t>
         </is>
       </c>
     </row>
@@ -1718,21 +1804,41 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Engage only</t>
+          <t>Spotlight</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>No new post. 15 minutes: reply to comments and DMs, comment on 5 posts from small business owners, answer 1 question in a Facebook group, Quora or Reddit.</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
+          <t>Service spotlight: website redesign and migration</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Week 3 (Oct 26 to Nov 01)/Day 20 Sat Oct 31 Spotlight Service spotlight website redesign and</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/website-redesign/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1743,7 +1849,7 @@
           <t>Sun 01 Nov</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Engage only</t>
         </is>
@@ -1995,21 +2101,41 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Engage only</t>
+          <t>Spotlight</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>No new post. 15 minutes: reply to comments and DMs, comment on 5 posts from small business owners, answer 1 question in a Facebook group, Quora or Reddit.</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
+          <t>Service spotlight: WordPress and online store development</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Week 4 (Nov 02 to Nov 08)/Day 27 Sat Nov 07 Spotlight Service spotlight WordPress and online</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/wordpress-development/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -2020,7 +2146,7 @@
           <t>Sun 08 Nov</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Engage only</t>
         </is>
@@ -2129,14 +2255,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>8 carousels, 5 reels, 9 pins, 53 uploads</t>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>8 carousels, 5 reels, 9 pins, 4 service spotlights, 65 uploads</t>
         </is>
       </c>
     </row>
@@ -2147,23 +2273,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2175,7 +2305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2249,12 +2379,12 @@
           <t>Tips</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="L1" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="M1" s="17" t="inlineStr">
         <is>
           <t>Post link (after posting)</t>
         </is>
@@ -2269,7 +2399,7 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -2325,12 +2455,12 @@
           <t>Upload the PDF as a Document. Title: Why is your WordPress site slow? 5 fixes.</t>
         </is>
       </c>
-      <c r="L2" s="18" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M2" s="18" t="n"/>
+      <c r="M2" s="19" t="n"/>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -2341,7 +2471,7 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
@@ -2396,12 +2526,12 @@
           <t>Alt text: Seven-slide guide to why WordPress sites are slow: too many scripts, no page cache, heavy images, render-blocking CSS and fonts, and nobody checking the score, with the free Vyntic Speed Optimizer plugin.</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M3" s="18" t="n"/>
+      <c r="M3" s="19" t="n"/>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="6" t="n">
@@ -2412,7 +2542,7 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
@@ -2465,12 +2595,12 @@
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M4" s="18" t="n"/>
+      <c r="M4" s="19" t="n"/>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -2481,7 +2611,7 @@
           <t>Tue 13 Oct 2026</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
@@ -2514,7 +2644,7 @@
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>TITLE: How to Pass the Core Web Vitals Assessment
-DESCRIPTION: How to pass the Core Web Vitals assessment: LCP, INP and CLS explained in plain English, with the fixes that move the score. A free guide from Vyntic Studio.
+DESCRIPTION: How to pass the Core Web Vitals assessment: LCP, INP and CLS explained in plain English, with the fixes that move the score. A free guide from Vyntic Studio. Want it done for you? Vyntic Studio offers website speed optimization.
 BOARD: Website Speed Tips</t>
         </is>
       </c>
@@ -2528,12 +2658,12 @@
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L5" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M5" s="18" t="n"/>
+      <c r="M5" s="19" t="n"/>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="6" t="n">
@@ -2544,7 +2674,7 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -2593,12 +2723,12 @@
           <t>Add reel-cover.jpg as the video thumbnail.</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L6" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M6" s="18" t="n"/>
+      <c r="M6" s="19" t="n"/>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -2609,7 +2739,7 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>YouTube Shorts</t>
         </is>
@@ -2655,12 +2785,12 @@
           <t>Paste the title and the description separately.</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M7" s="18" t="n"/>
+      <c r="M7" s="19" t="n"/>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="6" t="n">
@@ -2671,7 +2801,7 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
@@ -2724,12 +2854,12 @@
           <t>Choose reel-cover.jpg as the cover. Turn on auto captions. reel-silent.mp4 is the music-only version.</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L8" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M8" s="18" t="n"/>
+      <c r="M8" s="19" t="n"/>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -2740,7 +2870,7 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
@@ -2793,12 +2923,12 @@
           <t>Same caption as Instagram. Tick "Share to Facebook" in Instagram, or post it in Meta Business Suite.</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M9" s="18" t="n"/>
+      <c r="M9" s="19" t="n"/>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="6" t="n">
@@ -2809,7 +2939,7 @@
           <t>Thu 15 Oct 2026</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
@@ -2842,7 +2972,7 @@
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TITLE: Free WordPress Speed Plugin
-DESCRIPTION: Vyntic Speed Optimizer: a free WordPress speed plugin with page cache, delayed JavaScript, WebP images and a weekly PageSpeed report. No account or API key.
+DESCRIPTION: Vyntic Speed Optimizer: a free WordPress speed plugin with page cache, delayed JavaScript, WebP images and a weekly PageSpeed report. No account or API key. Need more speed? Vyntic Studio also offers hands-on website speed optimization.
 BOARD: WordPress Plugins</t>
         </is>
       </c>
@@ -2856,12 +2986,12 @@
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M10" s="18" t="n"/>
+      <c r="M10" s="19" t="n"/>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -2872,7 +3002,7 @@
           <t>Fri 16 Oct 2026</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
@@ -2927,12 +3057,12 @@
           <t>Upload the PDF as a Document. Title: WordPress 7.1.3 is out: update without breaking your site.</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M11" s="18" t="n"/>
+      <c r="M11" s="19" t="n"/>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="6" t="n">
@@ -2943,7 +3073,7 @@
           <t>Fri 16 Oct 2026</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
@@ -2996,12 +3126,12 @@
           <t>Alt text: Six-slide guide to updating to WordPress 7.1.3 safely: backup first, update on staging, then plugins and theme, then test forms and checkout, plus Vyntic care plans.</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M12" s="18" t="n"/>
+      <c r="M12" s="19" t="n"/>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -3012,7 +3142,7 @@
           <t>Fri 16 Oct 2026</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
@@ -3064,53 +3194,262 @@
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M13" s="18" t="n"/>
+      <c r="M13" s="19" t="n"/>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Sat 17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>9:00 AM ET</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>6:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Week 1 (Oct 12 to Oct 18)/Day 06 Sat Oct 17 Spotlight Service spotlight website design and</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Most small business websites look fine and do nothing.
+No calls. No form fills. No bookings. Just a nice brochure.
+When we design a website, we start with one question: what should a visitor do next? Then every page is built around that.
+What's included:
+• Custom design, not a template
+• Fast, mobile first and SEO ready
+• Built for Google and AI search
+• You own the site, the files and every login
+• 30 days of support after launch
+Starter sites from $1,490 (up to 5 pages). Business sites from $2,990 (up to 12 pages, with service and location pages).
+Tell us about your project and get a written scope with a fixed price within two business days: https://vyntic.studio/services/web-design/
+#WebDesign #SmallBusiness #WordPress</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/web-design/</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Post as a single image. Reply to every comment within the first hour.</t>
+        </is>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Sat 17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>12:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>9:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Week 1 (Oct 12 to Oct 18)/Day 06 Sat Oct 17 Spotlight Service spotlight website design and</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Need a website that actually brings in customers? 🖥️
+We design and build websites for small businesses:
+✅ Custom design, not a template
+✅ Fast and mobile first
+✅ Built for Google and AI search
+✅ You own the site and every login
+Starter sites from $1,490. Business sites from $2,990.
+Free quote: link in bio 👆
+#webdesign #websitedesign #smallbusiness #wordpress #webdesigner #smallbusinessowner #websitedesigner #webdevelopment #vynticstudio</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Link in bio</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Alt text: Vyntic Studio service spotlight: website design and development, custom design, fast and SEO ready, built for Google and AI search, starter sites from $1,490. Put https://vyntic.studio/services/web-design/ in your bio link for the weekend.</t>
+        </is>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Sat 17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>1:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>10:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Photo post</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Week 1 (Oct 12 to Oct 18)/Day 06 Sat Oct 17 Spotlight Service spotlight website design and</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Your website should bring in customers, not just look nice. 🖥️
+✅ Custom design, not a template
+✅ Fast, mobile first and SEO ready
+✅ Built for Google and AI search
+✅ You own the site and every login
+Starter sites from $1,490 · Business sites from $2,990
+Starter sites from $1,490 and business sites from $2,990. Get a free quote:
+👉 https://vyntic.studio/services/web-design/</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/web-design/</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Pin this post to the top of your Page until the next spotlight.</t>
+        </is>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Mon 19 Oct 2026</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 08 Mon Oct 19 Carousel AI Overviews are taking your clicks</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Ranking number 1 on Google is not what it used to be.
 Ahrefs found that the top result gets about 34.5% fewer clicks when an AI Overview appears above it. For question searches, Google now answers before anyone visits a website.
@@ -3126,63 +3465,63 @@
 #SEO #AIOverviews #AISearch</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: AI Overviews are taking your clicks: what to do now.</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L17" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="M17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Mon 19 Oct 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 08 Mon Oct 19 Carousel AI Overviews are taking your clicks</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Ranking #1 is not enough anymore 😬
 Google's AI Overviews answer the question before anyone clicks. Ahrefs found the top result gets about 34.5% fewer clicks when one shows.
@@ -3197,63 +3536,63 @@
 #seo #aioverviews #aisearch #googleseo #digitalmarketing #smallbusiness #marketingtips #localseo #webdesign #vynticstudio</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Alt text: Seven-slide guide to Google AI Overviews: the click impact, answer-first content, FAQ and schema, mentions on other sites, and winning the click.</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L18" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n"/>
-    </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="M18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Mon 19 Oct 2026</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 08 Mon Oct 19 Carousel AI Overviews are taking your clicks</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Google's AI Overviews now answer questions before anyone clicks a website. Here is how to stay visible. 🔎
 Swipe through:
@@ -3266,126 +3605,126 @@
 👉 https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L16" s="18" t="inlineStr">
+      <c r="L19" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M16" s="18" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="M19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Tue 20 Oct 2026</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 09 Tue Oct 20 Pin How to Get Recommended by ChatGPT</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>TITLE: How to Get Recommended by ChatGPT
-DESCRIPTION: How to get your business recommended by ChatGPT, Gemini and Google AI Overviews. A practical AI search guide for small businesses from Vyntic Studio.
+DESCRIPTION: How to get your business recommended by ChatGPT, Gemini and Google AI Overviews. A practical AI search guide for small businesses from Vyntic Studio. Want it done for you? Vyntic Studio offers AI search visibility services.
 BOARD: AI Search and SEO</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/get-recommended-by-chatgpt/</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L17" s="18" t="inlineStr">
+      <c r="L20" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M17" s="18" t="n"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="M20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="150" customHeight="1">
+      <c r="A21" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Video post</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 10 Wed Oct 21 Reel Is ChatGPT recommending your business</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Ask ChatGPT for the best dentist, plumber or lawyer in your city.
 Is your business in the answer?
@@ -3398,125 +3737,125 @@
 #AISearch #LocalSEO #SmallBusiness</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/get-recommended-by-chatgpt/</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>Add reel-cover.jpg as the video thumbnail.</t>
         </is>
       </c>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="L21" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="M21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="150" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>YouTube Shorts</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>11:00 AM ET</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>8:00 PM PKT</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 10 Wed Oct 21 Reel Is ChatGPT recommending your business</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>TITLE: Is ChatGPT Recommending Your Business? #shorts
 DESCRIPTION: 3 steps to show up when people ask AI who to call. Full guide: https://vyntic.studio/get-recommended-by-chatgpt/</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/get-recommended-by-chatgpt/</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>Paste the title and the description separately.</t>
         </is>
       </c>
-      <c r="L19" s="18" t="inlineStr">
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="6" t="n">
+      <c r="M22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 10 Wed Oct 21 Reel Is ChatGPT recommending your business</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4 + reel-cover.jpg</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Is ChatGPT recommending your business? 🤖
 Ask it for the best business like yours in your city. Are you in the answer?
@@ -3528,63 +3867,63 @@
 #aisearch #chatgpt #localseo #seo #smallbusiness #smallbusinesstips #digitalmarketing #marketingtips #vynticstudio</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>Choose reel-cover.jpg as the cover. Turn on auto captions. reel-silent.mp4 is the music-only version.</t>
         </is>
       </c>
-      <c r="L20" s="18" t="inlineStr">
+      <c r="L23" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M20" s="18" t="n"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="6" t="n">
+      <c r="M23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 10 Wed Oct 21 Reel Is ChatGPT recommending your business</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Is ChatGPT recommending your business? 🤖
 Ask it for the best business like yours in your city. Are you in the answer?
@@ -3596,126 +3935,126 @@
 #aisearch #chatgpt #localseo #seo #smallbusiness #smallbusinesstips #digitalmarketing #marketingtips #vynticstudio</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/get-recommended-by-chatgpt/</t>
         </is>
       </c>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>Same caption as Instagram. Tick "Share to Facebook" in Instagram, or post it in Meta Business Suite.</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="L24" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="6" t="n">
+      <c r="M24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Thu 22 Oct 2026</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 11 Thu Oct 22 Pin Local SEO Guide for Small Businesses</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>TITLE: Local SEO Guide for Small Businesses
-DESCRIPTION: A local SEO guide for small businesses: Google Business Profile, reviews, local pages and citations, so you show up in Google Maps. Free from Vyntic Studio.
+DESCRIPTION: A local SEO guide for small businesses: Google Business Profile, reviews, local pages and citations, so you show up in Google Maps. Free from Vyntic Studio. Want it done for you? See Vyntic Studio's local SEO services.
 BOARD: Local SEO Tips</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/local-seo-guide/</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L22" s="18" t="inlineStr">
+      <c r="L25" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="M25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Fri 23 Oct 2026</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 12 Fri Oct 23 Carousel SEO vs GEO in 2026 what actually changed</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Every week someone tells us SEO is dead because of AI.
 Our client data says otherwise. People who are ready to buy still search Google, and the local pack still sends calls.
@@ -3732,63 +4071,63 @@
 #SEO #GEO #AISearch</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/seo-services/</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: SEO vs GEO in 2026: what actually changed.</t>
         </is>
       </c>
-      <c r="L23" s="18" t="inlineStr">
+      <c r="L26" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="6" t="n">
+      <c r="M26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Fri 23 Oct 2026</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 12 Fri Oct 23 Carousel SEO vs GEO in 2026 what actually changed</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>SEO vs GEO: what actually changed in 2026? 🤔
 ✅ SEO still brings the buyers
@@ -3800,63 +4139,63 @@
 #seo #geo #aisearch #chatgpt #digitalmarketing #googleseo #marketingtips #smallbusiness #contentmarketing #vynticstudio</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>Alt text: Seven-slide comparison of SEO and GEO in 2026: what still works, what generative engine optimization adds, and how to measure AI visibility.</t>
         </is>
       </c>
-      <c r="L24" s="18" t="inlineStr">
+      <c r="L27" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="M27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Fri 23 Oct 2026</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Week 2 (Oct 19 to Oct 25)/Day 12 Fri Oct 23 Carousel SEO vs GEO in 2026 what actually changed</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Is SEO dead because of AI? No, but it changed. Here is SEO vs GEO in 2026. 🤔
 Swipe through:
@@ -3869,63 +4208,272 @@
 👉 https://vyntic.studio/services/seo-services/</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/seo-services/</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L25" s="18" t="inlineStr">
+      <c r="L28" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="6" t="n">
+      <c r="M28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Sat 24 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>9:00 AM ET</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>6:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Week 2 (Oct 19 to Oct 25)/Day 13 Sat Oct 24 Spotlight Service spotlight local SEO and lead</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Local businesses lose customers in two places:
+1. People can't find them on Google Maps
+2. When someone does call or fill in a form, nobody follows up fast enough
+We fix both:
+• Google Business Profile optimization: categories, services, photos, posts
+• Local SEO: a page for every service and area you cover
+• Review requests and reply templates your team will actually use
+• GoHighLevel automations, so every lead gets a reply in minutes
+Category and detail fixes can help within weeks. Reviews, photos and posts build results over two to three months.
+Local SEO: https://vyntic.studio/services/local-seo/
+Google Business Profile: https://vyntic.studio/services/google-business-profile-optimization/
+GoHighLevel setup: https://vyntic.studio/services/gohighlevel/
+#LocalSEO #GoogleBusinessProfile #SmallBusiness</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/local-seo/</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Post as a single image. Reply to every comment within the first hour.</t>
+        </is>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Sat 24 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>12:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>9:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Week 2 (Oct 19 to Oct 25)/Day 13 Sat Oct 24 Spotlight Service spotlight local SEO and lead</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Get found locally. Follow up every lead. 📍
+✅ Google Business Profile optimized
+✅ A page for every service and area
+✅ Review requests your team will use
+✅ Automatic follow-up, so no lead goes cold
+For plumbers, dentists, roofers, law firms and every local business.
+Book a free call: link in bio 👆
+#localseo #googlebusinessprofile #googlemaps #smallbusiness #localbusiness #gohighlevel #leadgeneration #marketingtips #vynticstudio</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Link in bio</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Alt text: Vyntic Studio service spotlight: local SEO, Google Business Profile optimization, review requests and GoHighLevel lead follow-up automations. Put https://vyntic.studio/services/local-seo/ in your bio link for the weekend.</t>
+        </is>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Sat 24 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>1:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>10:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Photo post</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Week 2 (Oct 19 to Oct 25)/Day 13 Sat Oct 24 Spotlight Service spotlight local SEO and lead</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Found on Google Maps, and every lead followed up within minutes. That's what we set up for local businesses. 📍
+✅ Google Business Profile optimized
+✅ Pages for every service and area
+✅ Review requests your team will use
+✅ Automatic lead follow-up
+Written scope with a fixed price in 2 business days
+Local SEO, Google Business Profile and GoHighLevel automations:
+👉 https://vyntic.studio/services/local-seo/</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/local-seo/</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Pin this post to the top of your Page until the next spotlight.</t>
+        </is>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Mon 26 Oct 2026</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 15 Mon Oct 26 Carousel Googles spam update just finished 5</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>Google's September 2026 spam update finished rolling out on 8 October.
 If your traffic dropped in the last few weeks, these are the 5 things we check first:
@@ -3940,63 +4488,63 @@
 #SEO #GoogleUpdate #SpamUpdate</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/free-audit/</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="K32" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: Google's spam update just finished: 5 things that get sites hit.</t>
         </is>
       </c>
-      <c r="L26" s="18" t="inlineStr">
+      <c r="L32" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M26" s="18" t="n"/>
-    </row>
-    <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="6" t="n">
+      <c r="M32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Mon 26 Oct 2026</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 15 Mon Oct 26 Carousel Googles spam update just finished 5</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Google's spam update just finished ⚠️
 These 5 things put sites at risk:
@@ -4010,63 +4558,63 @@
 #seo #googleupdate #googleseo #spamupdate #digitalmarketing #smallbusiness #seotips #websitetips #marketingtips #vynticstudio</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
         <is>
           <t>Alt text: Seven-slide guide to Google's September 2026 spam update: mass-produced pages, expired domain abuse, hidden links, doorway pages and what to do if traffic dropped.</t>
         </is>
       </c>
-      <c r="L27" s="18" t="inlineStr">
+      <c r="L33" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M27" s="18" t="n"/>
-    </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="6" t="n">
+      <c r="M33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Mon 26 Oct 2026</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 15 Mon Oct 26 Carousel Googles spam update just finished 5</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>Google's September spam update finished on 8 October. Here are 5 things that get sites hit. ⚠️
 Swipe through:
@@ -4079,126 +4627,126 @@
 👉 https://vyntic.studio/free-audit/</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/free-audit/</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L28" s="18" t="inlineStr">
+      <c r="L34" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="6" t="n">
+      <c r="M34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Tue 27 Oct 2026</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 16 Tue Oct 27 Pin Google Business Profile Guide</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>TITLE: Google Business Profile Guide
-DESCRIPTION: Google Business Profile guide: categories, services, photos, reviews and posts that help you rank in Google Maps. A free, practical guide from Vyntic Studio.
+DESCRIPTION: Google Business Profile guide: categories, services, photos, reviews and posts that help you rank in Google Maps. A free, practical guide from Vyntic Studio. Want it done for you? Vyntic Studio offers Google Business Profile optimization.
 BOARD: Local SEO Tips</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/google-business-profile-guide/</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L29" s="18" t="inlineStr">
+      <c r="L35" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="6" t="n">
+      <c r="M35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Video post</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 17 Wed Oct 28 Reel Website horror story the 12 second</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>A website horror story for Halloween week. 🎃
 A homepage that takes 12 seconds to load. Usually it is the same three monsters:
@@ -4210,125 +4758,125 @@
 #WebsiteSpeed #WordPress #Halloween</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/website-speed-optimization/</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>Add reel-cover.jpg as the video thumbnail.</t>
         </is>
       </c>
-      <c r="L30" s="18" t="inlineStr">
+      <c r="L36" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="6" t="n">
+      <c r="M36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>YouTube Shorts</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>11:00 AM ET</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>8:00 PM PKT</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 17 Wed Oct 28 Reel Website horror story the 12 second</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>TITLE: Website Horror Story: The 12 Second Homepage #shorts
 DESCRIPTION: An 8 MB slider, 47 plugins and no cache. Here is the fix. https://vyntic.studio/services/website-speed-optimization/</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/website-speed-optimization/</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
         <is>
           <t>Paste the title and the description separately.</t>
         </is>
       </c>
-      <c r="L31" s="18" t="inlineStr">
+      <c r="L37" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="6" t="n">
+      <c r="M37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 17 Wed Oct 28 Reel Website horror story the 12 second</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4 + reel-cover.jpg</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>Website horror story 🎃
 A homepage that takes 12 seconds to load. The usual monsters:
@@ -4340,63 +4888,63 @@
 #halloween #websitespeed #wordpress #webdesign #pagespeed #wordpresstips #smallbusiness #websitetips #vynticstudio</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>Choose reel-cover.jpg as the cover. Turn on auto captions. reel-silent.mp4 is the music-only version.</t>
         </is>
       </c>
-      <c r="L32" s="18" t="inlineStr">
+      <c r="L38" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="6" t="n">
+      <c r="M38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 17 Wed Oct 28 Reel Website horror story the 12 second</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>Website horror story 🎃
 A homepage that takes 12 seconds to load. The usual monsters:
@@ -4408,126 +4956,126 @@
 #halloween #websitespeed #wordpress #webdesign #pagespeed #wordpresstips #smallbusiness #websitetips #vynticstudio</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/website-speed-optimization/</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>Same caption as Instagram. Tick "Share to Facebook" in Instagram, or post it in Meta Business Suite.</t>
         </is>
       </c>
-      <c r="L33" s="18" t="inlineStr">
+      <c r="L39" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M33" s="18" t="n"/>
-    </row>
-    <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="6" t="n">
+      <c r="M39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Thu 29 Oct 2026</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 18 Thu Oct 29 Pin Website Redesign Checklist</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>TITLE: Website Redesign Checklist
-DESCRIPTION: Website redesign checklist: goals, content, SEO and launch steps so your new site does not lose traffic. A free checklist from Vyntic Studio.
+DESCRIPTION: Website redesign checklist: goals, content, SEO and launch steps so your new site does not lose traffic. A free checklist from Vyntic Studio. Planning a redesign? Vyntic Studio redesigns websites without losing rankings.
 BOARD: Web Design Tips</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-redesign-checklist/</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L34" s="18" t="inlineStr">
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M34" s="18" t="n"/>
-    </row>
-    <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="6" t="n">
+      <c r="M40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Fri 30 Oct 2026</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>6:00 PM PKT</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 19 Fri Oct 30 Carousel 7 Google Business Profile fixes before</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Your Google Business Profile is probably seen more often than your website.
 Before the holiday rush, these 7 fixes take about 10 minutes:
@@ -4539,68 +5087,69 @@
 6. Weekly posts
 7. Answers in Q and A
 The slides show what to check for each one.
-Full guide: https://vyntic.studio/google-business-profile-guide/
+Want it done for you? We optimize Google Business Profiles: https://vyntic.studio/services/google-business-profile-optimization/
+Free guide: https://vyntic.studio/google-business-profile-guide/
 Which one have you been putting off?
 #LocalSEO #GoogleBusinessProfile #SmallBusiness</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>https://vyntic.studio/google-business-profile-guide/</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/google-business-profile-optimization/</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: 7 Google Business Profile fixes before the holidays.</t>
         </is>
       </c>
-      <c r="L35" s="18" t="inlineStr">
+      <c r="L41" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M35" s="18" t="n"/>
-    </row>
-    <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="6" t="n">
+      <c r="M41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="150" customHeight="1">
+      <c r="A42" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Fri 30 Oct 2026</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 19 Fri Oct 30 Carousel 7 Google Business Profile fixes before</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-8.png</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>7 Google Business Profile fixes in 10 minutes ⏱️
 Do these before the holiday rush:
@@ -4612,67 +5161,67 @@
 6. Weekly posts
 7. Q and A
 Swipe for the checklist 👉 Save it 📌
-Full guide: link in bio.
+Want it done for you? Link in bio.
 #localseo #googlebusinessprofile #googlemaps #smallbusiness #smallbusinesstips #localbusiness #marketingtips #seo #shoplocal #vynticstudio</t>
         </is>
       </c>
-      <c r="J36" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr">
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>Alt text: Eight-slide checklist of seven Google Business Profile fixes before the holidays: holiday hours, primary category, services and offers, weekly photos, reviews and replies, posts and Q and A.</t>
         </is>
       </c>
-      <c r="L36" s="18" t="inlineStr">
+      <c r="L42" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M36" s="18" t="n"/>
-    </row>
-    <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="6" t="n">
+      <c r="M42" s="19" t="n"/>
+    </row>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Fri 30 Oct 2026</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Week 3 (Oct 26 to Nov 01)/Day 19 Fri Oct 30 Carousel 7 Google Business Profile fixes before</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-8.png</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Clocks change on 1 November and the holidays are coming. 7 quick fixes for your Google Business Profile. ⏱️
 Swipe through:
@@ -4683,67 +5232,276 @@
 ✅ Reviews and replies
 ✅ Weekly posts
 ✅ Q and A answers
-Our full Google Business Profile guide:
-👉 https://vyntic.studio/google-business-profile-guide/</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>https://vyntic.studio/google-business-profile-guide/</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
+Want it done for you? We set up and optimize Google Business Profiles:
+👉 https://vyntic.studio/services/google-business-profile-optimization/</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/google-business-profile-optimization/</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L37" s="18" t="inlineStr">
+      <c r="L43" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M37" s="18" t="n"/>
-    </row>
-    <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="6" t="n">
+      <c r="M43" s="19" t="n"/>
+    </row>
+    <row r="44" ht="150" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Sat 31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>9:00 AM ET</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>6:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Week 3 (Oct 26 to Nov 01)/Day 20 Sat Oct 31 Spotlight Service spotlight website redesign and</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>The scariest thing about a website redesign? 🎃
+Waking up a week after launch to find your Google traffic cut in half.
+It happens when old pages vanish without redirects, titles and schema get lost, and nobody checks Search Console after launch.
+How we redesign and migrate sites:
+• Every old URL mapped and redirected
+• SEO, titles and schema carried over
+• Search Console watched daily for the first weeks
+• A fresh design built to convert better
+Moving from Wix, Squarespace or Webflow to WordPress? Same process: https://vyntic.studio/services/website-migration/
+Most small business redesigns fall between $1,490 and $2,990, and stores start from $4,990.
+https://vyntic.studio/services/website-redesign/
+#WebsiteRedesign #SEO #WebDesign</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/website-redesign/</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Post as a single image. Reply to every comment within the first hour.</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Sat 31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>12:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>9:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Week 3 (Oct 26 to Nov 01)/Day 20 Sat Oct 31 Spotlight Service spotlight website redesign and</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>The scariest thing about a redesign? Losing your Google traffic 🎃
+How we redesign without that:
+✅ Every old URL redirected
+✅ SEO, titles and schema carried over
+✅ Search Console watched after launch
+✅ A fresh design that converts better
+Also moving sites from Wix, Squarespace or Webflow to WordPress.
+Free quote: link in bio 👆
+#websiteredesign #webdesign #seo #wordpress #websitemigration #smallbusiness #webdesigner #halloween #vynticstudio</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Link in bio</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Alt text: Vyntic Studio service spotlight: website redesign and migration with every URL redirected, SEO carried over and Search Console monitored after launch. Put https://vyntic.studio/services/website-redesign/ in your bio link for the weekend.</t>
+        </is>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="n"/>
+    </row>
+    <row r="46" ht="150" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Sat 31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>1:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>10:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Photo post</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Week 3 (Oct 26 to Nov 01)/Day 20 Sat Oct 31 Spotlight Service spotlight website redesign and</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>The scariest thing about a website redesign? Losing your Google traffic overnight. 🎃 Here's how we avoid it.
+✅ Every old URL mapped and redirected
+✅ SEO, titles and schema carried over
+✅ Search Console watched after launch
+✅ A fresh design that converts better
+Most redesigns $1,490 to $2,990 · Stores from $4,990
+Website redesigns and migrations from Vyntic Studio:
+👉 https://vyntic.studio/services/website-redesign/</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/website-redesign/</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Pin this post to the top of your Page until the next spotlight.</t>
+        </is>
+      </c>
+      <c r="L46" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M46" s="19" t="n"/>
+    </row>
+    <row r="47" ht="150" customHeight="1">
+      <c r="A47" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Mon 02 Nov 2026</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 22 Mon Nov 02 Carousel Black Friday is 27 November website</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Black Friday is on 27 November. If your website is part of your sales, now is the time to check it, not the week before.
 The checklist we run with ecommerce clients:
@@ -4758,63 +5516,63 @@
 #BlackFriday #Ecommerce #SmallBusiness</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/landing-page-design/</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr">
+      <c r="K47" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: Black Friday is 27 November: website checklist.</t>
         </is>
       </c>
-      <c r="L38" s="18" t="inlineStr">
+      <c r="L47" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M38" s="18" t="n"/>
-    </row>
-    <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="6" t="n">
+      <c r="M47" s="19" t="n"/>
+    </row>
+    <row r="48" ht="150" customHeight="1">
+      <c r="A48" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Mon 02 Nov 2026</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 22 Mon Nov 02 Carousel Black Friday is 27 November website</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>Is your website ready for Black Friday? 🛍️
 27 November is close. Check these now:
@@ -4828,63 +5586,63 @@
 #blackfriday #bfcm #ecommerce #smallbusiness #woocommerce #onlinestore #ecommercetips #smallbusinesstips #webdesign #vynticstudio</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K48" s="6" t="inlineStr">
         <is>
           <t>Alt text: Seven-slide Black Friday website checklist: speed, checkout, an offer landing page, stock and emails, and backup and support.</t>
         </is>
       </c>
-      <c r="L39" s="18" t="inlineStr">
+      <c r="L48" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M39" s="18" t="n"/>
-    </row>
-    <row r="40" ht="150" customHeight="1">
-      <c r="A40" s="6" t="n">
+      <c r="M48" s="19" t="n"/>
+    </row>
+    <row r="49" ht="150" customHeight="1">
+      <c r="A49" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Mon 02 Nov 2026</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>11:00 PM PKT</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 22 Mon Nov 02 Carousel Black Friday is 27 November website</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Black Friday is on 27 November. Is your website ready? 🛍️
 Swipe through:
@@ -4897,126 +5655,126 @@
 👉 https://vyntic.studio/services/landing-page-design/</t>
         </is>
       </c>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/landing-page-design/</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L40" s="18" t="inlineStr">
+      <c r="L49" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M40" s="18" t="n"/>
-    </row>
-    <row r="41" ht="150" customHeight="1">
-      <c r="A41" s="6" t="n">
+      <c r="M49" s="19" t="n"/>
+    </row>
+    <row r="50" ht="150" customHeight="1">
+      <c r="A50" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Tue 03 Nov 2026</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>8:00 PM PKT</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 23 Tue Nov 03 Pin How Much Does a Website Cost</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>TITLE: How Much Does a Website Cost?
-DESCRIPTION: How much does a website cost in 2026? Real price ranges for freelancer, agency and ecommerce websites, plus hosting and maintenance. Free guide from Vyntic Studio.
+DESCRIPTION: How much does a website cost in 2026? Real price ranges for freelancer, agency and ecommerce websites, plus hosting and maintenance. Free guide from Vyntic Studio. Vyntic Studio builds small business websites from $1,490.
 BOARD: Web Design Tips</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-cost/</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L41" s="18" t="inlineStr">
+      <c r="L50" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M41" s="18" t="n"/>
-    </row>
-    <row r="42" ht="150" customHeight="1">
-      <c r="A42" s="6" t="n">
+      <c r="M50" s="19" t="n"/>
+    </row>
+    <row r="51" ht="150" customHeight="1">
+      <c r="A51" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Video post</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 24 Wed Nov 04 Reel Your checkout is losing sales</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Black Friday is on 27 November, and most stores lose sales at the very last step.
 3 checkout fixes that are worth doing this week:
@@ -5028,125 +5786,125 @@
 #Ecommerce #BlackFriday #WooCommerce</t>
         </is>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ecommerce-development/</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
+      <c r="K51" s="6" t="inlineStr">
         <is>
           <t>Add reel-cover.jpg as the video thumbnail.</t>
         </is>
       </c>
-      <c r="L42" s="18" t="inlineStr">
+      <c r="L51" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M42" s="18" t="n"/>
-    </row>
-    <row r="43" ht="150" customHeight="1">
-      <c r="A43" s="6" t="n">
+      <c r="M51" s="19" t="n"/>
+    </row>
+    <row r="52" ht="150" customHeight="1">
+      <c r="A52" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>YouTube Shorts</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>11:00 AM ET</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 24 Wed Nov 04 Reel Your checkout is losing sales</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>TITLE: 3 Checkout Fixes Before Black Friday #shorts
 DESCRIPTION: Guest checkout, fewer fields, one-tap pay. https://vyntic.studio/services/ecommerce-development/</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ecommerce-development/</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>Paste the title and the description separately.</t>
         </is>
       </c>
-      <c r="L43" s="18" t="inlineStr">
+      <c r="L52" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M43" s="18" t="n"/>
-    </row>
-    <row r="44" ht="150" customHeight="1">
-      <c r="A44" s="6" t="n">
+      <c r="M52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="150" customHeight="1">
+      <c r="A53" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 24 Wed Nov 04 Reel Your checkout is losing sales</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4 + reel-cover.jpg</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Your checkout is losing sales 🛒
 3 fixes before Black Friday:
@@ -5158,63 +5916,63 @@
 #blackfriday #ecommerce #woocommerce #onlinestore #ecommercetips #smallbusiness #shopify #conversionrate #vynticstudio</t>
         </is>
       </c>
-      <c r="J44" s="6" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
+      <c r="K53" s="6" t="inlineStr">
         <is>
           <t>Choose reel-cover.jpg as the cover. Turn on auto captions. reel-silent.mp4 is the music-only version.</t>
         </is>
       </c>
-      <c r="L44" s="18" t="inlineStr">
+      <c r="L53" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M44" s="18" t="n"/>
-    </row>
-    <row r="45" ht="150" customHeight="1">
-      <c r="A45" s="6" t="n">
+      <c r="M53" s="19" t="n"/>
+    </row>
+    <row r="54" ht="150" customHeight="1">
+      <c r="A54" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>11:00 PM PKT</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 24 Wed Nov 04 Reel Your checkout is losing sales</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>Your checkout is losing sales 🛒
 3 fixes before Black Friday:
@@ -5226,126 +5984,126 @@
 #blackfriday #ecommerce #woocommerce #onlinestore #ecommercetips #smallbusiness #shopify #conversionrate #vynticstudio</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ecommerce-development/</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
+      <c r="K54" s="6" t="inlineStr">
         <is>
           <t>Same caption as Instagram. Tick "Share to Facebook" in Instagram, or post it in Meta Business Suite.</t>
         </is>
       </c>
-      <c r="L45" s="18" t="inlineStr">
+      <c r="L54" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M45" s="18" t="n"/>
-    </row>
-    <row r="46" ht="150" customHeight="1">
-      <c r="A46" s="6" t="n">
+      <c r="M54" s="19" t="n"/>
+    </row>
+    <row r="55" ht="150" customHeight="1">
+      <c r="A55" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Thu 05 Nov 2026</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>8:00 PM PKT</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 25 Thu Nov 05 Pin Squarespace vs Wix vs WordPress</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>TITLE: Squarespace vs Wix vs WordPress
-DESCRIPTION: Squarespace vs Wix vs WordPress: which website builder is best for your business in 2026? An honest comparison from Vyntic Studio.
+DESCRIPTION: Squarespace vs Wix vs WordPress: which website builder is best for your business in 2026? An honest comparison from Vyntic Studio. Vyntic Studio builds on WordPress, Wix, Squarespace and Webflow.
 BOARD: WordPress Tips</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/wix-vs-wordpress/</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
+      <c r="K55" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L46" s="18" t="inlineStr">
+      <c r="L55" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M46" s="18" t="n"/>
-    </row>
-    <row r="47" ht="150" customHeight="1">
-      <c r="A47" s="6" t="n">
+      <c r="M55" s="19" t="n"/>
+    </row>
+    <row r="56" ht="150" customHeight="1">
+      <c r="A56" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Fri 06 Nov 2026</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Document post (carousel)</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 26 Fri Nov 06 Carousel Shoppers now ask AI what to buy</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>linkedin-carousel.pdf</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>More shoppers now skip the search bar and ask ChatGPT, Gemini or Google's AI Mode what to buy.
 So the question for online stores this Black Friday is: when someone asks AI for "the best X for Y", are your products in the answer?
@@ -5361,63 +6119,63 @@
 #Ecommerce #AISearch #BlackFriday</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr">
+      <c r="K56" s="6" t="inlineStr">
         <is>
           <t>Upload the PDF as a Document. Title: Shoppers now ask AI what to buy.</t>
         </is>
       </c>
-      <c r="L47" s="18" t="inlineStr">
+      <c r="L56" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M47" s="18" t="n"/>
-    </row>
-    <row r="48" ht="150" customHeight="1">
-      <c r="A48" s="6" t="n">
+      <c r="M56" s="19" t="n"/>
+    </row>
+    <row r="57" ht="150" customHeight="1">
+      <c r="A57" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Fri 06 Nov 2026</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Carousel post</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 26 Fri Nov 06 Carousel Shoppers now ask AI what to buy</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>Shoppers now ask AI what to buy 🤖🛒
 To get your products recommended:
@@ -5431,63 +6189,63 @@
 #ecommerce #aisearch #chatgpt #blackfriday #onlinestore #ecommercetips #seo #smallbusiness #woocommerce #vynticstudio</t>
         </is>
       </c>
-      <c r="J48" s="6" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="K57" s="6" t="inlineStr">
         <is>
           <t>Alt text: Seven-slide guide to getting products recommended by AI shopping assistants: clear product pages, product schema, reviews, buying-question content and fast pages.</t>
         </is>
       </c>
-      <c r="L48" s="18" t="inlineStr">
+      <c r="L57" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M48" s="18" t="n"/>
-    </row>
-    <row r="49" ht="150" customHeight="1">
-      <c r="A49" s="6" t="n">
+      <c r="M57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="150" customHeight="1">
+      <c r="A58" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Fri 06 Nov 2026</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>11:00 PM PKT</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Photo post (multiple photos)</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Week 4 (Nov 02 to Nov 08)/Day 26 Fri Nov 06 Carousel Shoppers now ask AI what to buy</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>slide-1.png to slide-7.png</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>More shoppers now ask ChatGPT and Google's AI Mode what to buy. Here is how to get your products recommended. 🤖
 Swipe through:
@@ -5500,63 +6258,270 @@
 👉 https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/services/ai-search-visibility/</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K58" s="6" t="inlineStr">
         <is>
           <t>Share it to 1 or 2 relevant Facebook groups if their rules allow.</t>
         </is>
       </c>
-      <c r="L49" s="18" t="inlineStr">
+      <c r="L58" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M49" s="18" t="n"/>
-    </row>
-    <row r="50" ht="150" customHeight="1">
-      <c r="A50" s="6" t="n">
+      <c r="M58" s="19" t="n"/>
+    </row>
+    <row r="59" ht="150" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>9:00 AM ET</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>7:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Week 4 (Nov 02 to Nov 08)/Day 27 Sat Nov 07 Spotlight Service spotlight WordPress and online</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Black Friday is three weeks away. If your store struggled last year, now is the time to plan the next one.
+What we build:
+• Custom WordPress sites that stay fast
+• WooCommerce and Shopify stores built to convert
+• Security hardening, updates and daily backups from day one
+• Care plans from $99 a month, so it stays that way
+Custom WordPress from $1,490. Stores from $4,990.
+WordPress development: https://vyntic.studio/services/wordpress-development/
+WooCommerce: https://vyntic.studio/services/woocommerce-development/
+Shopify: https://vyntic.studio/services/shopify-development/
+#WordPress #WooCommerce #Shopify</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/wordpress-development/</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>Post as a single image. Reply to every comment within the first hour.</t>
+        </is>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="150" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>12:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>10:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Image post</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Week 4 (Nov 02 to Nov 08)/Day 27 Sat Nov 07 Spotlight Service spotlight WordPress and online</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>Custom WordPress and online stores 🛒
+✅ Clean, fast custom WordPress
+✅ WooCommerce or Shopify stores that convert
+✅ Hardening, updates and daily backups
+✅ Care plans from $99 a month
+Custom WordPress from $1,490. Stores from $4,990.
+Free quote: link in bio 👆
+#wordpress #woocommerce #shopify #ecommerce #webdevelopment #wordpressdeveloper #onlinestore #smallbusiness #vynticstudio</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Link in bio</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>Alt text: Vyntic Studio service spotlight: custom WordPress development, WooCommerce and Shopify stores and care plans from $99 a month. Put https://vyntic.studio/services/wordpress-development/ in your bio link for the weekend.</t>
+        </is>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M60" s="19" t="n"/>
+    </row>
+    <row r="61" ht="150" customHeight="1">
+      <c r="A61" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Sat 07 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>1:00 PM ET</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>11:00 PM PKT</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Photo post</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Week 4 (Nov 02 to Nov 08)/Day 27 Sat Nov 07 Spotlight Service spotlight WordPress and online</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>spotlight.png</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Planning a new website or online store? Here's what we build. 🛒
+✅ Clean, fast custom WordPress
+✅ WooCommerce or Shopify stores
+✅ Hardening, updates, daily backups
+✅ Care plans from $99 a month
+Custom WordPress from $1,490 · Stores from $4,990
+WordPress, WooCommerce and Shopify development from Vyntic Studio:
+👉 https://vyntic.studio/services/wordpress-development/</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>https://vyntic.studio/services/wordpress-development/</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Pin this post to the top of your Page until the next spotlight.</t>
+        </is>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="150" customHeight="1">
+      <c r="A62" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C62" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>9:00 AM ET</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>7:00 PM PKT</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>Video post</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Week 5 (Nov 09 to Nov 10)/Day 29 Mon Nov 09 Reel How much does a website cost in 2026</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>"How much does a website cost?" is the question we get most.
 The honest answer depends on three things:
@@ -5568,125 +6533,125 @@
 #WebDesign #SmallBusiness #WebsiteCost</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="J62" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-cost-calculator/</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
+      <c r="K62" s="6" t="inlineStr">
         <is>
           <t>Add reel-cover.jpg as the video thumbnail.</t>
         </is>
       </c>
-      <c r="L50" s="18" t="inlineStr">
+      <c r="L62" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M50" s="18" t="n"/>
-    </row>
-    <row r="51" ht="150" customHeight="1">
-      <c r="A51" s="6" t="n">
+      <c r="M62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="150" customHeight="1">
+      <c r="A63" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>YouTube Shorts</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>11:00 AM ET</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>9:00 PM PKT</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Week 5 (Nov 09 to Nov 10)/Day 29 Mon Nov 09 Reel How much does a website cost in 2026</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>TITLE: How Much Does a Website Cost in 2026? #shorts
 DESCRIPTION: Pages, features and content decide the price. Free calculator: https://vyntic.studio/website-cost-calculator/</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
+      <c r="J63" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-cost-calculator/</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr">
+      <c r="K63" s="6" t="inlineStr">
         <is>
           <t>Paste the title and the description separately.</t>
         </is>
       </c>
-      <c r="L51" s="18" t="inlineStr">
+      <c r="L63" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M51" s="18" t="n"/>
-    </row>
-    <row r="52" ht="150" customHeight="1">
-      <c r="A52" s="6" t="n">
+      <c r="M63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="150" customHeight="1">
+      <c r="A64" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="C52" s="17" t="inlineStr">
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>12:00 PM ET</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>10:00 PM PKT</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Week 5 (Nov 09 to Nov 10)/Day 29 Mon Nov 09 Reel How much does a website cost in 2026</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4 + reel-cover.jpg</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>How much does a website cost in 2026? 💸
 It depends on 3 things:
@@ -5698,63 +6663,63 @@
 #webdesign #websitecost #smallbusiness #websitedesign #wordpress #smallbusinesstips #entrepreneur #webdesigner #vynticstudio</t>
         </is>
       </c>
-      <c r="J52" s="6" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>Link in bio</t>
         </is>
       </c>
-      <c r="K52" s="6" t="inlineStr">
+      <c r="K64" s="6" t="inlineStr">
         <is>
           <t>Choose reel-cover.jpg as the cover. Turn on auto captions. reel-silent.mp4 is the music-only version.</t>
         </is>
       </c>
-      <c r="L52" s="18" t="inlineStr">
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="150" customHeight="1">
-      <c r="A53" s="6" t="n">
+      <c r="M64" s="19" t="n"/>
+    </row>
+    <row r="65" ht="150" customHeight="1">
+      <c r="A65" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C65" s="18" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>1:00 PM ET</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>11:00 PM PKT</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>Reel</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Week 5 (Nov 09 to Nov 10)/Day 29 Mon Nov 09 Reel How much does a website cost in 2026</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>reel-voiceover.mp4</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>How much does a website cost in 2026? 💸
 It depends on 3 things:
@@ -5766,89 +6731,89 @@
 #webdesign #websitecost #smallbusiness #websitedesign #wordpress #smallbusinesstips #entrepreneur #webdesigner #vynticstudio</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr">
+      <c r="J65" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-cost-calculator/</t>
         </is>
       </c>
-      <c r="K53" s="6" t="inlineStr">
+      <c r="K65" s="6" t="inlineStr">
         <is>
           <t>Same caption as Instagram. Tick "Share to Facebook" in Instagram, or post it in Meta Business Suite.</t>
         </is>
       </c>
-      <c r="L53" s="18" t="inlineStr">
+      <c r="L65" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M53" s="18" t="n"/>
-    </row>
-    <row r="54" ht="150" customHeight="1">
-      <c r="A54" s="6" t="n">
+      <c r="M65" s="19" t="n"/>
+    </row>
+    <row r="66" ht="150" customHeight="1">
+      <c r="A66" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Tue 10 Nov 2026</t>
         </is>
       </c>
-      <c r="C54" s="17" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>10:00 AM ET</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>8:00 PM PKT</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>Pin</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Week 5 (Nov 09 to Nov 10)/Day 30 Tue Nov 10 Pin How Much Does a Website Redesign Cost</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>pin.png</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>TITLE: How Much Does a Website Redesign Cost?
-DESCRIPTION: How much does a website redesign cost in 2026? Price ranges and what drives the cost, so you can budget with confidence. Free guide from Vyntic Studio.
+DESCRIPTION: How much does a website redesign cost in 2026? Price ranges and what drives the cost, so you can budget with confidence. Free guide from Vyntic Studio. Vyntic Studio redesigns most small business sites for $1,490 to $2,990.
 BOARD: Web Design Tips</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="J66" s="10" t="inlineStr">
         <is>
           <t>https://vyntic.studio/website-redesign-cost/</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr">
+      <c r="K66" s="6" t="inlineStr">
         <is>
           <t>Paste the link in the "Link" field so the pin sends visitors to the article.</t>
         </is>
       </c>
-      <c r="L54" s="18" t="inlineStr">
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="M54" s="18" t="n"/>
+      <c r="M66" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
-  <conditionalFormatting sqref="L2:L54">
+  <autoFilter ref="A1:M66"/>
+  <conditionalFormatting sqref="L2:L66">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>L2="Posted"</formula>
     </cfRule>
@@ -5857,7 +6822,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"To do,Scheduled,Posted,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5874,34 +6839,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
